--- a/已融合_准入清单.xlsx
+++ b/已融合_准入清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new qingzanggaoyuan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABA6C03-B924-4E4E-93CE-12C767B73FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3540E105-ACE0-4B39-8E24-A4CDD441ED26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="250">
   <si>
     <t>省</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>管控单元分类</t>
-  </si>
-  <si>
-    <t>格尔木市生态保护红线青海格尔木胡杨林省级自然保护区</t>
   </si>
   <si>
     <t>青海省</t>
@@ -1260,6 +1257,24 @@
   </si>
   <si>
     <t>格尔木市生态保护红线青海格尔木昆仑山国家级地质自然公园</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.执行海西州生态环境管控要求中第二条关 于生态保护红线空间布局约束的准入要求。 2.执行海西州生态环境管控要求中第十一条关于自然保护区空间布局约束的准入要求。 3.执行海西州生态环境管控要求中第三十一条关于柴达木盆地空间布局约束的准入要求。 (注：第二条的具体要求为：生态保护红线原则上按禁止开发区域的要求进行管理。严禁不符合主体功能定位的各类开发活动，严禁任意改变用途。（一）规范管控对生态功能不造成破坏的有限人为活动。生态保护红线是国土空间规划中的重要管控边界，生态保护红线内自然保护地核心保护区外，禁止开发性、生产性建设活动，在符合法律法规的前提下，仅允许以下对生态功能不造成破坏的有限人为活动。生态保护红线内自然保护区、风景名胜区、饮用水水源保护区等区域，依照法律法规执行。
+1.管护巡护、保护执法、科学研究、调查监测、测绘导航、防灾减灾救灾、军事国防、疫情防控等活动及相关的必要设施修筑。
+2.原住居民和其他合法权益主体，允许在不扩大现有建设用地、耕地、水产养殖规模和放牧强度（符合草畜平衡管理规定）的前提下，开展种植、放牧、捕捞、养殖等活动，修筑生产生活设施。
+3.经依法批准的考古调查发掘、古生物化石调查发掘、标本采集和文物保护活动。
+4.按规定对人工商品林进行抚育采伐，或以提升森林质量、优化栖息地、建设生物防火隔离带等为目的的树种更新，依法开展的竹林采伐经营。5.不破坏生态功能的适度参观旅游、科普宣教及符合相关规划的配套性服务设施和相关的必要公共设施建设及维护。
+6.必须且无法避让、符合县级以上国土空间规划的线性基础设施、通讯和防洪、供水设施建设和船舶航行、航道疏浚清淤等活动；已有的合法水利、交通运输等设施运行维护改造。
+7.地质调查与矿产资源勘查开采。包括：基础地质调查和战略性矿产资源远景调查等公益性工作；铀矿勘查开采活动，可办理矿业权登记；已依法设立的油气探矿权继续勘查活动，可办理探矿权延续、变更（不含扩大勘查区块范围）、保留、注销，当发现可供开采油气资源并探明储量时，可将开采拟占用的地表范围依照国家相关规定调出生态保护红线；已依法设立的油气采矿权不扩大用地用海范围，继续开采，可办理采矿权延续、变更（不含扩大矿区范围）、注销；已依法设立的矿泉水和地热采矿权，在不超出已经核定的生产规模、不新增生产设施的前提下继续开采，可办理采矿权延续、变更（不含扩大矿区范围）、注销；已依法设立和新立铬、铜、镍、锂、钴、锆、钾盐、（中）重稀土矿等战略性矿产探矿权开展勘查活动，可办理探矿权登记，因国家战略需要开展开采活动的，可办理采矿权登记。上述勘查开采活动，应落实减缓生态环境影响措施，严格执行绿色勘查、开采及矿山环境生态修复相关要求。
+8.依据县级以上国土空间规划和生态保护修复专项规划开展的生态修复。
+9.法律法规规定允许的其他人为活动。
+（二）加强有限人为活动管理。上述生态保护红线管控范围内有限人为活动，涉及新增建设用地审批的，在报批农用地转用、土地征收开发利用时，附省级人民政府出具符合生态保护红线内允许有限人为活动的认定意见；不涉及新增建设用地审批的，按有关规定进行管理，无明确规定的由省级人民政府制定具体监管办法。上述活动涉及自然保护地的，应征求林业和草原主管部门或自然保护地管理机构意见。
+（三）有序处理历史遗留问题。生态保护红线经国务院批准后，对需逐步有序退出的矿业权等，由省级人民政府按照尊重历史、实事求是的原则，结合实际制定退出计划，明确时序安排、补偿安置、生态修复等要求，确保生态安全和社会稳定。鼓励有条件的地方通过租赁、置换、赎买等方式，对人工商品林实行统一管护，并将重要生态区位的人工商品林按规定逐步转为公益林。零星分布的已有水电、风电、光伏能设施，按照相关法律法规规定进行管理，严禁扩大现有规模与范围，项目到期后由建设单位负责做好生态修复。)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>格尔木市生态保护红线青海格尔木胡杨林省级自然保护区</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1677,7 +1692,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1692,507 +1707,507 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>4</v>
+        <v>249</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E4" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="259.2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="144" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="201.6" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:232" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:232" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:232" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:232" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:232" ht="201.6" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:232" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:232" ht="144" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:232" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E24" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:232" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E25" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:232" s="10" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>7</v>
-      </c>
       <c r="E26" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
@@ -2423,2520 +2438,2521 @@
     </row>
     <row r="27" spans="1:232" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:232" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:232" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:232" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:232" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="E31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:232" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="230.4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="100.8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="259.2" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="E52" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="216" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="172.8" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="172.8" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B79" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="5" t="s">
+      <c r="D79" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="E79" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F79" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="172.8" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="201.6" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="216" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F93" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="172.8" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E97" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F97" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B99" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>164</v>
-      </c>
       <c r="E99" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E100" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F103" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F110" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="172.8" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F112" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="B113" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E120" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F120" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F121" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F121" s="5" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B122" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D122" s="6" t="s">
+      <c r="E122" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F122" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F123" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E123" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" s="5" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="216" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F124" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F125" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F126" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F127" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="144" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F131" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F131" s="5" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F132" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F133" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F133" s="5" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B134" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>216</v>
-      </c>
       <c r="E134" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B135" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>218</v>
-      </c>
       <c r="E135" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="244.8" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F139" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F140" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F141" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E141" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F142" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F143" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F145" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F146" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="172.8" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="B147" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="100.8" x14ac:dyDescent="0.25">
       <c r="B148" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="57.6" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E151" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F151" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>